--- a/Documents/タスク一覧画面レイアウト.xlsx
+++ b/Documents/タスク一覧画面レイアウト.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s19\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B802B568-6D64-4E34-AA85-E350F900BEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FE9368-0C37-4CEA-B3CB-07DB56DB8D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -806,6 +806,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -821,35 +866,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -857,51 +887,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,12 +921,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2423,19 +2423,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="27" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -2447,48 +2447,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="48"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="29" t="s">
+      <c r="E2" s="45"/>
+      <c r="F2" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="35">
+      <c r="G2" s="45"/>
+      <c r="H2" s="27">
         <v>45807</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="39"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="48"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="23"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="40"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="41"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="33"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -3848,19 +3848,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="27" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -3872,67 +3872,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="48"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="29" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="29" t="s">
+      <c r="E2" s="45"/>
+      <c r="F2" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="35">
+      <c r="G2" s="45"/>
+      <c r="H2" s="27">
         <v>45807</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="39"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="48"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="23"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="40"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="48"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="23"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="40"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="32"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="58" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="54"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="60"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="58" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="20"/>
@@ -3943,22 +3943,22 @@
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
-      <c r="J6" s="43"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="59"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="48"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -3967,10 +3967,10 @@
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
-      <c r="J8" s="62"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="48"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -3979,10 +3979,10 @@
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="62"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="48"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -3991,10 +3991,10 @@
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="62"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="48"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -4003,10 +4003,10 @@
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
-      <c r="J11" s="62"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="48"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
@@ -4015,10 +4015,10 @@
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="62"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="48"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -4027,10 +4027,10 @@
       <c r="G13" s="23"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
-      <c r="J13" s="62"/>
+      <c r="J13" s="64"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="58" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="20"/>
@@ -4041,15 +4041,15 @@
       <c r="G14" s="20"/>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
-      <c r="J14" s="43"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="58" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21"/>
-      <c r="D15" s="42"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
@@ -4060,7 +4060,7 @@
       <c r="J15" s="14"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="58" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="20"/>
@@ -4077,95 +4077,95 @@
       <c r="G16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="65" t="s">
         <v>10</v>
       </c>
       <c r="I16" s="20"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="57"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="20"/>
       <c r="C17" s="21"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
-      <c r="H17" s="42"/>
+      <c r="H17" s="52"/>
       <c r="I17" s="20"/>
-      <c r="J17" s="43"/>
+      <c r="J17" s="53"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="57"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="42"/>
+      <c r="H18" s="52"/>
       <c r="I18" s="20"/>
-      <c r="J18" s="43"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="57"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="20"/>
       <c r="C19" s="21"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="42"/>
+      <c r="H19" s="52"/>
       <c r="I19" s="20"/>
-      <c r="J19" s="43"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="57"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="20"/>
       <c r="C20" s="21"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="42"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="20"/>
-      <c r="J20" s="43"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="57"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="20"/>
       <c r="C21" s="21"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="42"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="20"/>
-      <c r="J21" s="43"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="57"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="20"/>
       <c r="C22" s="21"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="42"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="20"/>
-      <c r="J22" s="43"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="56"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="53"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="50"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5146,17 +5146,10 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
@@ -5173,10 +5166,17 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
